--- a/reference/fixtures/Valoraciones_ficticias_EPS_1er_cuatrimestre_v0_3.xlsx
+++ b/reference/fixtures/Valoraciones_ficticias_EPS_1er_cuatrimestre_v0_3.xlsx
@@ -729,7 +729,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="22" t="str">
-        <x:v>Nueva</x:v>
+        <x:v>Ficticia</x:v>
       </x:c>
       <x:c r="B12" s="22" t="str">
         <x:v>Carla Cuatro</x:v>
